--- a/data/BaseScene.xlsx
+++ b/data/BaseScene.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BaseScene" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BaseScene" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D7" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D13" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D14" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D15" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D16" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D17" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D18" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D19" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D20" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
